--- a/results/result_2.xlsx
+++ b/results/result_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="result_2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result_2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,8 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>SELECT total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year DESC LIMIT 1</t>
+          <t>SELECT total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year DESC LIMIT 1;
+SELECT total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period = '2025Q3'</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -507,7 +508,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>[{"Q": "金花股份利润总额是多少", "A": {"content": "金花股份的利润总额为 **393.40万元**（单位：万元）。\n\n### 分析展开\n\n以下是对金花股份利润总额的详细分析：\n\n#### 1. **数据来源**\n- 根据SQL查询结果，金花股份最近一期（报告期包含“FY”的财务数据）的利润总额为 **393.40万元**，该数据来源于其最新的利润表（income_sheet）。\n\n#### 2. **数据准确性说明**\n- 查询结果中返回的金额为 **3934047.66**，单位为元，换算为万元即为 **393.40万元**，数据准确无误，符合财务报表的常规单位换算。\n\n#### 3. **行业背景与趋势分析**\n- 金花股份属于中药行业，该行业近年来受到政策支持、市场需求增长以及消费升级等因素的影响，整体呈现稳步发展的趋势。\n- 然而，中药行业的竞争也日趋激烈，部分企业面临成本上升、研发投入加大等压力。金花股份的利润总额为 **393.40万元**，表明其盈利能力尚可，但需结合其营收规模、行业地位及历史数据进一步分析。\n\n#### 4. **对比分析**\n- 若与同行业其他大型中药企业（如同仁堂、云南白药等）相比，金花股份的利润总额相对较低，这可能与其企业规模、产品结构、市场占有率等因素有关。\n- 但若与中小中药企业相比，金花股份的利润总额则处于中等偏上水平，说明其在成本控制和盈利能力方面表现尚可。\n\n#### 5. **数据异常说明**\n- 从数据本身来看，**393.40万元**的利润总额在中药行业中属于正常范围，未发现明显异常。不过，若该数据与金花股份历史财务数据相比有显著波动，可能需要进一步分析其经营状况的变化，如市场环境、产品结构调整、成本控制措施等。\n\n#### 6. **结论与建议**\n- **结论**：金花股份的利润总额为 **393.40万元**，表明其在当前经营周期内保持了一定的盈利水平。\n- **建议**：建议进一步分析其利润来源（如主营业务利润、投资收益等）及成本结构，以判断其盈利的可持续性。同时，可结合其营收、净利润率等指标，全面评估其财务健康状况和市场竞争力。"}, "sql": "SELECT total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year DESC LIMIT 1"}, {"Q": "2025年第三季度的", "A": {"content": "请问您想了解金花股份2025年第三季度的哪方面信息？"}}]</t>
+          <t>[{"Q": "金花股份利润总额是多少", "A": {"content": "根据查询结果，**未能获取到金花股份最新的利润总额数据**。\n\n### 📊 数据查询说明\n- 查询目标：金花股份（股票简称）的利润总额\n- 数据来源：合并利润表数据库（`income_sheet`）\n- 筛选条件：报表周期为“全年”（`%FY`），按年度降序取最新一条\n- 查询结果：**返回为空**\n\n### 🔍 可能原因\n1. **公司更名或证券代码变更**  \n   金花股份近年可能进行过重大资产重组或更名，导致数据库中无法以“金花股份”这一简称匹配到最新报表。例如，公司曾用名包括“金花企业(集团)股份有限公司”，若数据库记录的名称与此不一致，查询会返回空。\n\n2. **财务报告尚未披露**  \n   若当前处于财报披露窗口期之前，最新一期年报可能尚未入库，而历史年报中已无该简称对应的记录（例如旧数据被清理或归档）。\n\n3. **数据源口径问题**  \n   该数据库可能仅收录部分上市公司的财务数据，金花股份若因ST、暂停上市或业务调整等原因被移出统计范围，也会导致查无数据。\n\n### 💡 建议\n- 核实股票当前交易简称及代码（A股代码：600080），以准确名称重新查询。\n- 确认需要查询的具体年度，可尝试扩大时间范围或去除报告周期限制。\n- 若为持续跟踪该企业，建议通过上交所官网或巨潮资讯网直接查阅其最新财务报告中的“利润总额”项目。\n\n如果您能提供更精确的年份或确认公司当前准确简称，我可以为您进行更精准的查询分析。"}, "sql": "SELECT total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year DESC LIMIT 1"}, {"Q": "2025年第三季度的", "A": {"content": "很抱歉，根据数据库查询的结果，**目前无法提供金花股份2025年第三季度的利润总额数据**。  \n\n执行的SQL查询返回了空结果，这意味着在当前的财务数据系统中，**金花股份（股票简称）尚未披露或录入2025年Q3的利润表数据**。  \n\n---\n\n### 可能的原因分析  \n\n1. **财报尚未披露**  \n   - 中国A股上市公司季度报告的披露截止时间通常为季度结束后1个月内（如三季报不晚于10月31日）。  \n   - 如果当前时间早于2025年三季报的集中披露期（例如仍在10月或更早），数据未入库是正常现象。  \n\n2. **数据库收录延迟**  \n   - 即使公司已发布财报，数据从原始公告到被金融数据库抓取、清洗、入库也存在数小时到数天的延迟。  \n\n3. **公司特殊情形**  \n   - 若金花股份因重大事项（如重组、停牌、退市风险等）申请了延期披露，或发布了更正公告，也可能导致数据暂时缺失。  \n\n4. **查询条件匹配问题**  \n   - 确认输入的股票简称和报告期格式是否完全匹配（如“金花股份”是否带有ST、*ST等前缀，报告期是否为准确的“2025Q3”）。当前使用的条件为`stock_abbr = '金花股份' AND report_period = '2025Q3'`，若公司简称有变动，也可能命中失败。  \n\n---\n\n### 建议操作  \n\n- **等待财报发布**：您可以关注上交所或深交所官网，查看金花股份（600080）的预约披露时间表，在公告后重新查询。  \n- **查阅已披露数据**：可尝试查询更早的报告期（如2025Q2、2024Q4）作为近期利润水平的参考。  \n- **核对公司状态**：如果公司近期有更名、摘帽等情况，请使用最新的股票简称再次查询。  \n\n如有其他具体数据需求（如查看历史利润总额或同期对比），欢迎补充说明，我可以为您进一步分析。"}, "sql": "SELECT total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period = '2025Q3'"}]</t>
         </is>
       </c>
     </row>
@@ -524,17 +525,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>SELECT report_year, total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year DESC</t>
+          <t>SELECT report_period, total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year ASC</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>line (B1002_1_1.jpg)</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的", "A": {"content": "金花股份近几年的利润总额呈现**大幅波动**的趋势，其中2024年利润总额显著增长，而2022年利润总额极低，可能为数据异常或特殊情况所致。\n\n### 利润总额变化趋势分析\n\n以下为金花股份近几年的利润总额数据（单位：万元）：\n\n| 报告年份 | 利润总额（万元） |\n|----------|------------------|\n| 2025     | 3,934,047.66     |\n| 2024     | 9,249,809.58     |\n| 2023     | 3,859,654.77     |\n| 2022     | 4,288.7          |\n\n从数据来看，金花股份的利润总额在2022年仅为4,288.7万元，远低于其他年份，这可能是由于当年公司面临较大的经营压力或市场环境变化所致。2023年利润总额回升至3,859,654.77万元，但相比2024年的9,249,809.58万元仍有较大差距。2025年利润总额进一步下降至3,934,047.66万元，表明公司可能在2024年实现了阶段性业绩高峰，而2025年面临新的挑战或市场调整。\n\n### 数据异常说明\n\n2022年的利润总额（4,288.7万元）与其他年份相比明显偏低，这种数量级的差异可能由以下原因造成：\n- **财务数据录入错误**：可能是数据采集或录入过程中出现的误差。\n- **特殊事件影响**：如当年公司遭遇重大经营问题、政策调整、市场波动等。\n- **会计政策变更**：公司可能在2022年调整了会计政策，导致利润总额的计算方式发生变化。\n\n建议进一步核查2022年的财务数据，确认是否存在异常情况或特殊背景。\n\n### 结论与建议\n\n金花股份的利润总额在近几年内波动较大，2024年达到近年来的峰值，而2025年有所回落。这种波动可能与公司业务结构调整、市场环境变化或行业周期性有关。建议关注其后续财报，分析具体业务板块的贡献变化，并结合行业趋势进一步判断其未来发展方向。", "image": ["E:\\PyCharm\\taidibei\\results\\B1002_1_1.jpg"]}, "sql": "SELECT report_year, total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year DESC", "chart_type": "line"}]</t>
+          <t>[{"Q": "金花股份近几年的利润总额变化趋势是什么样的", "A": {"content": "很抱歉，根据当前执行的SQL查询，未能在数据库中获取到“金花股份”近几年的利润总额数据。查询返回结果为空。\n\n这种情况通常由以下几种原因导致，建议逐一排查：\n1.  **财务报告周期标识符不匹配**：SQL查询中使用的过滤条件 `report_period LIKE '%FY'` 旨在筛选年报数据。但部分数据源中，年报的报告期可能直接标识为年份（如“2023-12-31”）而非以“FY”结尾的字符串，导致筛选失效。\n2.  **股票简称或代码不一致**：数据库中的公司名称可能并非完全的“金花股份”，例如可能是“ST金花”（该公司曾于2021年被实施其他风险警示，后撤销）或使用其股票代码“600080.SH”进行存储。使用不准确的简称会导致查询不到数据。\n3.  **数据缺失**：目标数据库中可能暂未收录该上市公司近年度的完整财务数据。\n\n为了能为您提供准确的金花股份利润总额变化趋势分析，建议您：\n**协助修正并重新执行以下SQL查询，以排除报告期格式和股票简称的干扰：**\n\n```sql\n-- 尝试放宽报告期限制，并使用股票代码和简称同时匹配\nSELECT \n    report_period, \n    total_profit \nFROM \n    income_sheet \nWHERE \n    (stock_abbr LIKE '%金花%' OR stock_code = '600080') \n    AND end_date LIKE '%-12-31'  -- 使用更通用的年末日期匹配年报\nORDER BY \n    end_date ASC;\n```\n\n在获得准确数据后，我可以立即为您生成包含具体数值、变化趋势图表及专业分析的完整报告。"}, "sql": "SELECT report_period, total_profit FROM income_sheet WHERE stock_abbr = '金花股份' AND report_period LIKE '%FY' ORDER BY report_year ASC"}]</t>
         </is>
       </c>
     </row>
